--- a/data/Arisdorf/investment_decision/Arisdorf_SFH_from_2015_investment_decision.xlsx
+++ b/data/Arisdorf/investment_decision/Arisdorf_SFH_from_2015_investment_decision.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,12 +58,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,57 +441,57 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>scen_all_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>scale_MW</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>scen_all_candidate_unit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>scen_base_invested_available_unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>scale_MW</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>scen_base_candidate_unit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B2" t="n">
@@ -505,29 +506,29 @@
         <v>0.003</v>
       </c>
       <c r="E2" t="n">
-        <v>18158.49961690776</v>
+        <v>18146.21172969697</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>18158.49961690776</v>
+        <v>18146.21172969697</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>18158.49961690776</v>
+        <v>18146.21172969697</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>18158.49961690776</v>
+        <v>18146.21172969697</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B3" t="n">
@@ -542,33 +543,33 @@
         <v>0.003</v>
       </c>
       <c r="E3" t="n">
-        <v>18158.49961690776</v>
+        <v>18146.21172969697</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>18158.49961690776</v>
+        <v>18146.21172969697</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>18158.49961690776</v>
+        <v>18146.21172969697</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>18158.49961690776</v>
+        <v>18146.21172969697</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>102.6148236075947</v>
+        <v>110.8139366289805</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -579,33 +580,33 @@
         <v>0.003</v>
       </c>
       <c r="E4" t="n">
-        <v>18158.49961690776</v>
+        <v>18146.21172969697</v>
       </c>
       <c r="F4" t="n">
-        <v>101.6428728926817</v>
+        <v>103.1143378310346</v>
       </c>
       <c r="G4" t="n">
-        <v>18158.49961690776</v>
+        <v>18146.21172969697</v>
       </c>
       <c r="H4" t="n">
-        <v>104.2199147266073</v>
+        <v>103.8145938709894</v>
       </c>
       <c r="I4" t="n">
-        <v>18158.49961690776</v>
+        <v>18146.21172969697</v>
       </c>
       <c r="J4" t="n">
-        <v>102.2833825897766</v>
+        <v>110.4501483408031</v>
       </c>
       <c r="K4" t="n">
-        <v>18158.49961690776</v>
+        <v>18146.21172969697</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>111.8961443785454</v>
+        <v>114.0068503617944</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -616,33 +617,33 @@
         <v>0.003</v>
       </c>
       <c r="E5" t="n">
-        <v>18158.49961690776</v>
+        <v>18146.21172969697</v>
       </c>
       <c r="F5" t="n">
-        <v>112.1922779347602</v>
+        <v>103.8360466043794</v>
       </c>
       <c r="G5" t="n">
-        <v>18158.49961690776</v>
+        <v>18146.21172969697</v>
       </c>
       <c r="H5" t="n">
-        <v>113.3348626736163</v>
+        <v>105.3442896349704</v>
       </c>
       <c r="I5" t="n">
-        <v>18158.49961690776</v>
+        <v>18146.21172969697</v>
       </c>
       <c r="J5" t="n">
-        <v>113.3348626736163</v>
+        <v>114.0068503617944</v>
       </c>
       <c r="K5" t="n">
-        <v>18158.49961690776</v>
+        <v>18146.21172969697</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>111.8961443785454</v>
+        <v>114.0068503617944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -653,29 +654,29 @@
         <v>0.003</v>
       </c>
       <c r="E6" t="n">
-        <v>18158.49961690776</v>
+        <v>18146.21172969697</v>
       </c>
       <c r="F6" t="n">
-        <v>112.1922779347602</v>
+        <v>103.8360466043794</v>
       </c>
       <c r="G6" t="n">
-        <v>18158.49961690776</v>
+        <v>18146.21172969697</v>
       </c>
       <c r="H6" t="n">
-        <v>113.3348626736163</v>
+        <v>105.3442896349704</v>
       </c>
       <c r="I6" t="n">
-        <v>18158.49961690776</v>
+        <v>18146.21172969697</v>
       </c>
       <c r="J6" t="n">
-        <v>113.3348626736163</v>
+        <v>114.0068503617944</v>
       </c>
       <c r="K6" t="n">
-        <v>18158.49961690776</v>
+        <v>18146.21172969697</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B7" t="n">
@@ -690,29 +691,29 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>27.23774942536164</v>
+        <v>27.21931759454546</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>27.23774942536164</v>
+        <v>27.21931759454546</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>27.23774942536164</v>
+        <v>27.21931759454546</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>27.23774942536164</v>
+        <v>27.21931759454546</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B8" t="n">
@@ -727,29 +728,29 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>27.23774942536164</v>
+        <v>27.21931759454546</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>27.23774942536164</v>
+        <v>27.21931759454546</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>27.23774942536164</v>
+        <v>27.21931759454546</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>27.23774942536164</v>
+        <v>27.21931759454546</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B9" t="n">
@@ -764,29 +765,29 @@
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>27.23774942536164</v>
+        <v>27.21931759454546</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>27.23774942536164</v>
+        <v>27.21931759454546</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>27.23774942536164</v>
+        <v>27.21931759454546</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>27.23774942536164</v>
+        <v>27.21931759454546</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B10" t="n">
@@ -801,29 +802,29 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>27.23774942536164</v>
+        <v>27.21931759454546</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>27.23774942536164</v>
+        <v>27.21931759454546</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>27.23774942536164</v>
+        <v>27.21931759454546</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>27.23774942536164</v>
+        <v>27.21931759454546</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B11" t="n">
@@ -838,33 +839,33 @@
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>27.23774942536164</v>
+        <v>27.21931759454546</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>27.23774942536164</v>
+        <v>27.21931759454546</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>27.23774942536164</v>
+        <v>27.21931759454546</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>27.23774942536164</v>
+        <v>27.21931759454546</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.00668651328</v>
+        <v>0.00686278897874609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -890,18 +891,18 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.00668651328</v>
+        <v>0.00686278897874609</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.00668651328</v>
+        <v>0.00686278897874609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -927,18 +928,18 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.00668651328</v>
+        <v>0.00686278897874609</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.008653134832941176</v>
+        <v>0.009439783454117646</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,30 +953,30 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.008653134832941176</v>
+        <v>0.009439783454117646</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.008653134832941176</v>
+        <v>0.009439783454117646</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.008653134832941176</v>
+        <v>0.009439783454117646</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.009046459143529414</v>
+        <v>0.009439783454117646</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,30 +990,30 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.009046459143529414</v>
+        <v>0.009439783454117646</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.009046459143529414</v>
+        <v>0.009439783454117646</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.009046459143529414</v>
+        <v>0.009439783454117646</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.009046459143529414</v>
+        <v>0.009439783454117646</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,26 +1027,26 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.009046459143529414</v>
+        <v>0.009439783454117646</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.009046459143529414</v>
+        <v>0.009439783454117646</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.009046459143529414</v>
+        <v>0.009439783454117646</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B17" t="n">
@@ -1082,7 +1083,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B18" t="n">
@@ -1119,7 +1120,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B19" t="n">
@@ -1156,11 +1157,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>2.156978033315449</v>
+        <v>3.672714278869759</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,30 +1175,30 @@
         <v>7.020838944000002</v>
       </c>
       <c r="F20" t="n">
-        <v>2.156978033315449</v>
+        <v>3.672714278869759</v>
       </c>
       <c r="G20" t="n">
         <v>7.020838944000002</v>
       </c>
       <c r="H20" t="n">
-        <v>2.156978033315449</v>
+        <v>3.672714278869759</v>
       </c>
       <c r="I20" t="n">
         <v>7.020838944000002</v>
       </c>
       <c r="J20" t="n">
-        <v>2.156978033315449</v>
+        <v>3.672714278869759</v>
       </c>
       <c r="K20" t="n">
         <v>7.020838944000002</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>2.156978033315449</v>
+        <v>3.672714278869759</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,26 +1212,26 @@
         <v>7.020838944000002</v>
       </c>
       <c r="F21" t="n">
-        <v>2.156978033315449</v>
+        <v>3.672714278869759</v>
       </c>
       <c r="G21" t="n">
         <v>7.020838944000002</v>
       </c>
       <c r="H21" t="n">
-        <v>2.156978033315449</v>
+        <v>3.672714278869759</v>
       </c>
       <c r="I21" t="n">
         <v>7.020838944000002</v>
       </c>
       <c r="J21" t="n">
-        <v>2.156978033315449</v>
+        <v>3.672714278869759</v>
       </c>
       <c r="K21" t="n">
         <v>7.020838944000002</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B22" t="n">
@@ -1267,7 +1268,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B23" t="n">
@@ -1304,7 +1305,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B24" t="n">
@@ -1341,7 +1342,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B25" t="n">
@@ -1378,7 +1379,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B26" t="n">
@@ -1415,7 +1416,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B27" t="n">
@@ -1452,7 +1453,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B28" t="n">
@@ -1489,7 +1490,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B29" t="n">
@@ -1526,7 +1527,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B30" t="n">
@@ -1563,7 +1564,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B31" t="n">
@@ -1600,7 +1601,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B32" t="n">
@@ -1637,7 +1638,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B33" t="n">
@@ -1674,7 +1675,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B34" t="n">
@@ -1711,7 +1712,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B35" t="n">
@@ -1748,7 +1749,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B36" t="n">
@@ -1785,7 +1786,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B37" t="n">
@@ -1822,7 +1823,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B38" t="n">
@@ -1859,7 +1860,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B39" t="n">
@@ -1896,7 +1897,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B40" t="n">
@@ -1933,7 +1934,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B41" t="n">
@@ -1970,7 +1971,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B42" t="n">
@@ -2007,7 +2008,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B43" t="n">
@@ -2044,7 +2045,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B44" t="n">
@@ -2081,7 +2082,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B45" t="n">
@@ -2118,7 +2119,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B46" t="n">
@@ -2155,7 +2156,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B47" t="n">
@@ -2170,29 +2171,29 @@
         <v>0.017</v>
       </c>
       <c r="E47" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B48" t="n">
@@ -2207,29 +2208,29 @@
         <v>0.017</v>
       </c>
       <c r="E48" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B49" t="n">
@@ -2244,29 +2245,29 @@
         <v>0.017</v>
       </c>
       <c r="E49" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B50" t="n">
@@ -2281,29 +2282,29 @@
         <v>0.017</v>
       </c>
       <c r="E50" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B51" t="n">
@@ -2318,29 +2319,29 @@
         <v>0.017</v>
       </c>
       <c r="E51" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B52" t="n">
@@ -2355,29 +2356,29 @@
         <v>0.017</v>
       </c>
       <c r="E52" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B53" t="n">
@@ -2392,33 +2393,33 @@
         <v>0.017</v>
       </c>
       <c r="E53" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>2.351679326160209</v>
+        <v>0.88594552153171</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2429,33 +2430,33 @@
         <v>0.017</v>
       </c>
       <c r="E54" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F54" t="n">
-        <v>2.169393281608985</v>
+        <v>0.9541034576131053</v>
       </c>
       <c r="G54" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H54" t="n">
-        <v>2.348009337396792</v>
+        <v>0.88444362923897</v>
       </c>
       <c r="I54" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J54" t="n">
-        <v>2.169393281608985</v>
+        <v>0.990460652965965</v>
       </c>
       <c r="K54" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>5.146944309153945</v>
+        <v>3.815513600954933</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2466,33 +2467,33 @@
         <v>0.017</v>
       </c>
       <c r="E55" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F55" t="n">
-        <v>4.826845965530022</v>
+        <v>3.938183411142265</v>
       </c>
       <c r="G55" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H55" t="n">
-        <v>5.146944309153946</v>
+        <v>3.850700340327625</v>
       </c>
       <c r="I55" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J55" t="n">
-        <v>4.827293381283972</v>
+        <v>3.912003990738215</v>
       </c>
       <c r="K55" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>5.146944309153945</v>
+        <v>3.815513600954933</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2503,29 +2504,29 @@
         <v>0.017</v>
       </c>
       <c r="E56" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F56" t="n">
-        <v>4.826845965530022</v>
+        <v>3.938183411142264</v>
       </c>
       <c r="G56" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H56" t="n">
-        <v>5.146944309153945</v>
+        <v>3.850700340327625</v>
       </c>
       <c r="I56" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J56" t="n">
-        <v>4.827293381283972</v>
+        <v>3.912003990738215</v>
       </c>
       <c r="K56" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B57" t="n">
@@ -2540,29 +2541,29 @@
         <v>0.017</v>
       </c>
       <c r="E57" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B58" t="n">
@@ -2577,29 +2578,29 @@
         <v>0.017</v>
       </c>
       <c r="E58" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B59" t="n">
@@ -2614,29 +2615,29 @@
         <v>0.017</v>
       </c>
       <c r="E59" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B60" t="n">
@@ -2651,29 +2652,29 @@
         <v>0.017</v>
       </c>
       <c r="E60" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B61" t="n">
@@ -2688,29 +2689,29 @@
         <v>0.017</v>
       </c>
       <c r="E61" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2725,29 +2726,29 @@
         <v>0.017</v>
       </c>
       <c r="E62" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B63" t="n">
@@ -2762,33 +2763,33 @@
         <v>0.017</v>
       </c>
       <c r="E63" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>4.483926486670764</v>
+        <v>4.177412877389695</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2799,33 +2800,33 @@
         <v>0.017</v>
       </c>
       <c r="E64" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F64" t="n">
-        <v>4.687652620521542</v>
+        <v>4.27909903243946</v>
       </c>
       <c r="G64" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H64" t="n">
-        <v>4.452190053691259</v>
+        <v>4.333312036402829</v>
       </c>
       <c r="I64" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J64" t="n">
-        <v>4.673523730144447</v>
+        <v>4.080922487606413</v>
       </c>
       <c r="K64" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>4.483926486670764</v>
+        <v>4.177412877389695</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2836,33 +2837,33 @@
         <v>0.017</v>
       </c>
       <c r="E65" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F65" t="n">
-        <v>4.797492472437009</v>
+        <v>4.27909903243946</v>
       </c>
       <c r="G65" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H65" t="n">
-        <v>4.452190053691259</v>
+        <v>4.333312036402829</v>
       </c>
       <c r="I65" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J65" t="n">
-        <v>4.771840981561231</v>
+        <v>4.080922487606413</v>
       </c>
       <c r="K65" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>4.483926486670764</v>
+        <v>4.177412877389695</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2873,29 +2874,29 @@
         <v>0.017</v>
       </c>
       <c r="E66" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F66" t="n">
-        <v>4.797492472437009</v>
+        <v>4.27909903243946</v>
       </c>
       <c r="G66" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H66" t="n">
-        <v>4.452190053691259</v>
+        <v>4.333312036402829</v>
       </c>
       <c r="I66" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J66" t="n">
-        <v>4.771840981561231</v>
+        <v>4.080922487606413</v>
       </c>
       <c r="K66" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B67" t="n">
@@ -2910,29 +2911,29 @@
         <v>0.017</v>
       </c>
       <c r="E67" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B68" t="n">
@@ -2947,29 +2948,29 @@
         <v>0.017</v>
       </c>
       <c r="E68" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B69" t="n">
@@ -2984,29 +2985,29 @@
         <v>0.017</v>
       </c>
       <c r="E69" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B70" t="n">
@@ -3021,29 +3022,29 @@
         <v>0.017</v>
       </c>
       <c r="E70" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B71" t="n">
@@ -3058,29 +3059,29 @@
         <v>0.017</v>
       </c>
       <c r="E71" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B72" t="n">
@@ -3095,29 +3096,29 @@
         <v>0.017</v>
       </c>
       <c r="E72" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B73" t="n">
@@ -3132,29 +3133,29 @@
         <v>0.017</v>
       </c>
       <c r="E73" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B74" t="n">
@@ -3169,29 +3170,29 @@
         <v>0.017</v>
       </c>
       <c r="E74" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B75" t="n">
@@ -3206,29 +3207,29 @@
         <v>0.017</v>
       </c>
       <c r="E75" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B76" t="n">
@@ -3243,29 +3244,29 @@
         <v>0.017</v>
       </c>
       <c r="E76" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B77" t="n">
@@ -3280,29 +3281,29 @@
         <v>0.017</v>
       </c>
       <c r="E77" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B78" t="n">
@@ -3317,29 +3318,29 @@
         <v>0.017</v>
       </c>
       <c r="E78" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B79" t="n">
@@ -3354,29 +3355,29 @@
         <v>0.017</v>
       </c>
       <c r="E79" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B80" t="n">
@@ -3391,29 +3392,29 @@
         <v>0.017</v>
       </c>
       <c r="E80" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B81" t="n">
@@ -3428,25 +3429,25 @@
         <v>0.017</v>
       </c>
       <c r="E81" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>32.25510820010663</v>
+        <v>43.23557056610037</v>
       </c>
     </row>
   </sheetData>

--- a/data/Arisdorf/investment_decision/Arisdorf_SFH_from_2015_investment_decision.xlsx
+++ b/data/Arisdorf/investment_decision/Arisdorf_SFH_from_2015_investment_decision.xlsx
@@ -441,52 +441,52 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>scen_base_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>scale_MW</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>scen_base_candidate_unit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>scale_MW</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>scen_base_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>scen_base_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>110.8139366289805</v>
+        <v>40.21873166690213</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>18146.21172969697</v>
       </c>
       <c r="F4" t="n">
-        <v>103.1143378310346</v>
+        <v>43.45066417993723</v>
       </c>
       <c r="G4" t="n">
         <v>18146.21172969697</v>
       </c>
       <c r="H4" t="n">
-        <v>103.8145938709894</v>
+        <v>39.98365694523979</v>
       </c>
       <c r="I4" t="n">
         <v>18146.21172969697</v>
       </c>
       <c r="J4" t="n">
-        <v>110.4501483408031</v>
+        <v>43.4506641799371</v>
       </c>
       <c r="K4" t="n">
         <v>18146.21172969697</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>114.0068503617944</v>
+        <v>50.66220007031507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>18146.21172969697</v>
       </c>
       <c r="F5" t="n">
-        <v>103.8360466043794</v>
+        <v>67.60668261875226</v>
       </c>
       <c r="G5" t="n">
         <v>18146.21172969697</v>
       </c>
       <c r="H5" t="n">
-        <v>105.3442896349704</v>
+        <v>54.8255351785742</v>
       </c>
       <c r="I5" t="n">
         <v>18146.21172969697</v>
       </c>
       <c r="J5" t="n">
-        <v>114.0068503617944</v>
+        <v>63.9406652404444</v>
       </c>
       <c r="K5" t="n">
         <v>18146.21172969697</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>114.0068503617944</v>
+        <v>50.66220007031507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>18146.21172969697</v>
       </c>
       <c r="F6" t="n">
-        <v>103.8360466043794</v>
+        <v>67.60668261875226</v>
       </c>
       <c r="G6" t="n">
         <v>18146.21172969697</v>
       </c>
       <c r="H6" t="n">
-        <v>105.3442896349704</v>
+        <v>54.8255351785742</v>
       </c>
       <c r="I6" t="n">
         <v>18146.21172969697</v>
       </c>
       <c r="J6" t="n">
-        <v>114.0068503617944</v>
+        <v>63.9406652404444</v>
       </c>
       <c r="K6" t="n">
         <v>18146.21172969697</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Arisdorf_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Arisdorf_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>27.21931759454546</v>
+        <v>0.191301617977528</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>27.21931759454546</v>
+        <v>0.191301617977528</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>27.21931759454546</v>
+        <v>0.191301617977528</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>27.21931759454546</v>
+        <v>0.191301617977528</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Arisdorf_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Arisdorf_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>27.21931759454546</v>
+        <v>0.191301617977528</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>27.21931759454546</v>
+        <v>0.191301617977528</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>27.21931759454546</v>
+        <v>0.191301617977528</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>27.21931759454546</v>
+        <v>0.191301617977528</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Arisdorf_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Arisdorf_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>27.21931759454546</v>
+        <v>0.191301617977528</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>27.21931759454546</v>
+        <v>0.191301617977528</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>27.21931759454546</v>
+        <v>0.191301617977528</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>27.21931759454546</v>
+        <v>0.191301617977528</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Arisdorf_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Arisdorf_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>27.21931759454546</v>
+        <v>0.191301617977528</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>27.21931759454546</v>
+        <v>0.191301617977528</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>27.21931759454546</v>
+        <v>0.191301617977528</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>27.21931759454546</v>
+        <v>0.191301617977528</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Arisdorf_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Arisdorf_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>27.21931759454546</v>
+        <v>0.191301617977528</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>27.21931759454546</v>
+        <v>0.191301617977528</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>27.21931759454546</v>
+        <v>0.191301617977528</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>27.21931759454546</v>
+        <v>0.191301617977528</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.00686278897874609</v>
+        <v>0.003431394489373045</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.00668651328</v>
+        <v>0.003431394489373045</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00668651328</v>
+        <v>0.003933243105882353</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.00686278897874609</v>
+        <v>0.003933243105882353</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.00686278897874609</v>
+        <v>0.003431394489373045</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00668651328</v>
+        <v>0.003431394489373045</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00668651328</v>
+        <v>0.003933243105882353</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.00686278897874609</v>
+        <v>0.003933243105882353</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.009439783454117646</v>
+        <v>0.007473161901176471</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.009439783454117646</v>
+        <v>0.007473161901176471</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.009439783454117646</v>
+        <v>0.007473161901176471</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.009439783454117646</v>
+        <v>0.007473161901176471</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.009439783454117646</v>
+        <v>0.009046459143529414</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.009439783454117646</v>
+        <v>0.009046459143525018</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.009439783454117646</v>
+        <v>0.007866486211764711</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.009439783454117646</v>
+        <v>0.007866486211764711</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.009439783454117646</v>
+        <v>0.009046459143529402</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.009439783454117646</v>
+        <v>0.00904645914352506</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.009439783454117646</v>
+        <v>0.007866486211764711</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.009439783454117646</v>
+        <v>0.007866486211764711</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>3.672714278869759</v>
+        <v>2.003190868630889</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>7.020838944000002</v>
       </c>
       <c r="F20" t="n">
-        <v>3.672714278869759</v>
+        <v>2.226565566318465</v>
       </c>
       <c r="G20" t="n">
         <v>7.020838944000002</v>
       </c>
       <c r="H20" t="n">
-        <v>3.672714278869759</v>
+        <v>1.585283788630889</v>
       </c>
       <c r="I20" t="n">
         <v>7.020838944000002</v>
       </c>
       <c r="J20" t="n">
-        <v>3.672714278869759</v>
+        <v>1.585283788630889</v>
       </c>
       <c r="K20" t="n">
         <v>7.020838944000002</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>3.672714278869759</v>
+        <v>2.003190868630889</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>7.020838944000002</v>
       </c>
       <c r="F21" t="n">
-        <v>3.672714278869759</v>
+        <v>2.226565566318465</v>
       </c>
       <c r="G21" t="n">
         <v>7.020838944000002</v>
       </c>
       <c r="H21" t="n">
-        <v>3.672714278869759</v>
+        <v>1.585283788630889</v>
       </c>
       <c r="I21" t="n">
         <v>7.020838944000002</v>
       </c>
       <c r="J21" t="n">
-        <v>3.672714278869759</v>
+        <v>1.585283788630889</v>
       </c>
       <c r="K21" t="n">
         <v>7.020838944000002</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>1.67162832</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>7.020838944000002</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1.448253622312421</v>
       </c>
       <c r="G30" t="n">
         <v>7.020838944000002</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>2.0895354</v>
       </c>
       <c r="I30" t="n">
         <v>7.020838944000002</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>2.0895354</v>
       </c>
       <c r="K30" t="n">
         <v>7.020838944000002</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1.67162832</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>7.020838944000002</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1.448253622312421</v>
       </c>
       <c r="G31" t="n">
         <v>7.020838944000002</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2.0895354</v>
       </c>
       <c r="I31" t="n">
         <v>7.020838944000002</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>2.0895354</v>
       </c>
       <c r="K31" t="n">
         <v>7.020838944000002</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.88594552153171</v>
+        <v>1.351399420723008</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>43.23557056610037</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9541034576131053</v>
+        <v>1.221439701329734</v>
       </c>
       <c r="G54" t="n">
         <v>43.23557056610037</v>
       </c>
       <c r="H54" t="n">
-        <v>0.88444362923897</v>
+        <v>1.283907546965292</v>
       </c>
       <c r="I54" t="n">
         <v>43.23557056610037</v>
       </c>
       <c r="J54" t="n">
-        <v>0.990460652965965</v>
+        <v>1.221439701329736</v>
       </c>
       <c r="K54" t="n">
         <v>43.23557056610037</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>3.815513600954933</v>
+        <v>4.08059372297777</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>43.23557056610037</v>
       </c>
       <c r="F55" t="n">
-        <v>3.938183411142265</v>
+        <v>3.775291412207558</v>
       </c>
       <c r="G55" t="n">
         <v>43.23557056610037</v>
       </c>
       <c r="H55" t="n">
-        <v>3.850700340327625</v>
+        <v>4.005579580443244</v>
       </c>
       <c r="I55" t="n">
         <v>43.23557056610037</v>
       </c>
       <c r="J55" t="n">
-        <v>3.912003990738215</v>
+        <v>3.757638457809895</v>
       </c>
       <c r="K55" t="n">
         <v>43.23557056610037</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>3.815513600954933</v>
+        <v>4.08059372297777</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>43.23557056610037</v>
       </c>
       <c r="F56" t="n">
-        <v>3.938183411142264</v>
+        <v>3.775291412207558</v>
       </c>
       <c r="G56" t="n">
         <v>43.23557056610037</v>
       </c>
       <c r="H56" t="n">
-        <v>3.850700340327625</v>
+        <v>4.005579580443244</v>
       </c>
       <c r="I56" t="n">
         <v>43.23557056610037</v>
       </c>
       <c r="J56" t="n">
-        <v>3.912003990738215</v>
+        <v>3.757638457809895</v>
       </c>
       <c r="K56" t="n">
         <v>43.23557056610037</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>4.177412877389695</v>
+        <v>3.112734229300656</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>43.23557056610037</v>
       </c>
       <c r="F64" t="n">
-        <v>4.27909903243946</v>
+        <v>3.152506625567492</v>
       </c>
       <c r="G64" t="n">
         <v>43.23557056610037</v>
       </c>
       <c r="H64" t="n">
-        <v>4.333312036402829</v>
+        <v>3.186785881084649</v>
       </c>
       <c r="I64" t="n">
         <v>43.23557056610037</v>
       </c>
       <c r="J64" t="n">
-        <v>4.080922487606413</v>
+        <v>3.152506625567492</v>
       </c>
       <c r="K64" t="n">
         <v>43.23557056610037</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>4.177412877389695</v>
+        <v>3.112734229300656</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>43.23557056610037</v>
       </c>
       <c r="F65" t="n">
-        <v>4.27909903243946</v>
+        <v>3.269853944737023</v>
       </c>
       <c r="G65" t="n">
         <v>43.23557056610037</v>
       </c>
       <c r="H65" t="n">
-        <v>4.333312036402829</v>
+        <v>3.22991746042553</v>
       </c>
       <c r="I65" t="n">
         <v>43.23557056610037</v>
       </c>
       <c r="J65" t="n">
-        <v>4.080922487606413</v>
+        <v>3.398145105499813</v>
       </c>
       <c r="K65" t="n">
         <v>43.23557056610037</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>4.177412877389695</v>
+        <v>3.112734229300656</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>43.23557056610037</v>
       </c>
       <c r="F66" t="n">
-        <v>4.27909903243946</v>
+        <v>3.269853944737023</v>
       </c>
       <c r="G66" t="n">
         <v>43.23557056610037</v>
       </c>
       <c r="H66" t="n">
-        <v>4.333312036402829</v>
+        <v>3.22991746042553</v>
       </c>
       <c r="I66" t="n">
         <v>43.23557056610037</v>
       </c>
       <c r="J66" t="n">
-        <v>4.080922487606413</v>
+        <v>3.398145105499813</v>
       </c>
       <c r="K66" t="n">
         <v>43.23557056610037</v>
